--- a/output/Data and Chart Outputs/china_gacc_energy_imports_monthly.xlsx
+++ b/output/Data and Chart Outputs/china_gacc_energy_imports_monthly.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="Units" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Chart" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Chart - crude oil and refined p" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Chart - crude oil and product i" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Chart - coal imports" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Data" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Series" sheetId="6" state="visible" r:id="rId6"/>
@@ -321,7 +321,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>China crude oil and refined product imports (GACC customs) (to Aug/26)</a:t>
+              <a:t>China crude oil and product imports (GACC customs) (to Aug/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -336,7 +336,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Chart - crude oil and refined p'!B1</f>
+              <f>'Chart - crude oil and product i'!B1</f>
             </strRef>
           </tx>
           <spPr>
@@ -357,12 +357,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - crude oil and refined p'!$A$2:$A$68</f>
+              <f>'Chart - crude oil and product i'!$A$2:$A$68</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - crude oil and refined p'!$B$2:$B$68</f>
+              <f>'Chart - crude oil and product i'!$B$2:$B$68</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -372,7 +372,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Chart - crude oil and refined p'!C1</f>
+              <f>'Chart - crude oil and product i'!C1</f>
             </strRef>
           </tx>
           <spPr>
@@ -393,12 +393,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - crude oil and refined p'!$A$2:$A$68</f>
+              <f>'Chart - crude oil and product i'!$A$2:$A$68</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - crude oil and refined p'!$C$2:$C$68</f>
+              <f>'Chart - crude oil and product i'!$C$2:$C$68</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>crude oil and refined product imports</t>
+          <t>crude oil and product imports</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -5920,7 +5920,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>crude oil and refined product imports</t>
+          <t>crude oil and product imports</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">

--- a/output/Data and Chart Outputs/china_gacc_energy_imports_monthly.xlsx
+++ b/output/Data and Chart Outputs/china_gacc_energy_imports_monthly.xlsx
@@ -158,7 +158,8 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>China natural gas imports (GACC customs) (to Aug/26)</a:t>
+              <a:rPr sz="1200" b="1"/>
+              <a:t>China natural gas imports (GACC customs) (to Sep/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -188,12 +189,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$68</f>
+              <f>'Chart'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$68</f>
+              <f>'Chart'!$B$2:$B$69</f>
             </numRef>
           </val>
         </ser>
@@ -216,12 +217,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$68</f>
+              <f>'Chart'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$68</f>
+              <f>'Chart'!$C$2:$C$69</f>
             </numRef>
           </val>
         </ser>
@@ -321,7 +322,8 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>China crude oil and product imports (GACC customs) (to Aug/26)</a:t>
+              <a:rPr sz="1200" b="1"/>
+              <a:t>China crude oil and product imports (GACC customs) (to Sep/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -357,12 +359,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - crude oil and product i'!$A$2:$A$68</f>
+              <f>'Chart - crude oil and product i'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - crude oil and product i'!$B$2:$B$68</f>
+              <f>'Chart - crude oil and product i'!$B$2:$B$69</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -393,12 +395,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - crude oil and product i'!$A$2:$A$68</f>
+              <f>'Chart - crude oil and product i'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - crude oil and product i'!$C$2:$C$68</f>
+              <f>'Chart - crude oil and product i'!$C$2:$C$69</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -497,7 +499,8 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>China coal imports (GACC customs) (to Aug/26)</a:t>
+              <a:rPr sz="1200" b="1"/>
+              <a:t>China coal imports (GACC customs) (to Sep/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -533,12 +536,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - coal imports'!$A$2:$A$68</f>
+              <f>'Chart - coal imports'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - coal imports'!$B$2:$B$68</f>
+              <f>'Chart - coal imports'!$B$2:$B$69</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1059,7 +1062,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C68"/>
+  <dimension ref="A1:C69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1817,6 +1820,17 @@
       </c>
       <c r="C68" t="n">
         <v>5.17</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B69" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="C69" t="n">
+        <v>5.25</v>
       </c>
     </row>
   </sheetData>
@@ -1831,7 +1845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C68"/>
+  <dimension ref="A1:C69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2589,6 +2603,17 @@
       </c>
       <c r="C68" t="n">
         <v>2.25</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B69" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="C69" t="n">
+        <v>1.85</v>
       </c>
     </row>
   </sheetData>
@@ -2603,7 +2628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B68"/>
+  <dimension ref="A1:B69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3155,6 +3180,14 @@
       </c>
       <c r="B68" t="n">
         <v>42.09</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B69" t="n">
+        <v>43.37</v>
       </c>
     </row>
   </sheetData>
@@ -3169,7 +3202,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L68"/>
+  <dimension ref="A1:L69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5778,6 +5811,44 @@
       </c>
       <c r="L68" t="n">
         <v>5.17</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B69" t="n">
+        <v>43.37</v>
+      </c>
+      <c r="C69" t="n">
+        <v>4542.9</v>
+      </c>
+      <c r="D69" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="E69" t="n">
+        <v>24608.9</v>
+      </c>
+      <c r="F69" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="G69" t="n">
+        <v>1599.6</v>
+      </c>
+      <c r="H69" t="n">
+        <v>10.86</v>
+      </c>
+      <c r="I69" t="n">
+        <v>6346.4</v>
+      </c>
+      <c r="J69" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="K69" t="n">
+        <v>4155.6</v>
+      </c>
+      <c r="L69" t="n">
+        <v>5.25</v>
       </c>
     </row>
   </sheetData>
